--- a/Data/extension.xlsx
+++ b/Data/extension.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348BB22F-2050-409F-8697-091DD1454B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14A1729-08B3-4896-A58A-7FAD780B1C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -79,10 +90,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>936-937</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1025-1026</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -108,6 +115,10 @@
   </si>
   <si>
     <t>308-309</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>996-997</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -151,13 +162,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,272 +497,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1"/>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1" t="s">
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G10">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="H10">
         <v>18</v>
       </c>
-      <c r="C9" s="1">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>36</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11">
         <v>36</v>
       </c>
     </row>
